--- a/LoanOfficer-A/2023/58 thasana.xlsx
+++ b/LoanOfficer-A/2023/58 thasana.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5200</v>
+        <v>8800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>18800</v>
+        <v>15200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -863,9 +863,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45567</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -895,9 +901,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -927,9 +939,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -959,9 +977,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45570</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -991,9 +1015,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45571</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1023,9 +1053,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45572</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1055,9 +1091,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45573</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1087,9 +1129,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45574</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1119,9 +1167,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45575</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1151,9 +1205,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45577</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1183,9 +1243,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45577</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1215,9 +1281,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45581</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1247,9 +1319,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45581</v>
+      </c>
+      <c r="G15" s="4">
+        <v>200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1279,9 +1357,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45581</v>
+      </c>
+      <c r="G16" s="4">
+        <v>200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1683,9 +1767,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45563</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1709,9 +1799,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45564</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1735,9 +1831,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45565</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1761,9 +1863,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45566</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/58 thasana.xlsx
+++ b/LoanOfficer-A/2023/58 thasana.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8800</v>
+        <v>9200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15200</v>
+        <v>14800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1395,9 +1395,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45583</v>
+      </c>
+      <c r="G17" s="4">
+        <v>200</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1427,9 +1433,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45583</v>
+      </c>
+      <c r="G18" s="4">
+        <v>200</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
